--- a/app/reports/SY_research.xlsx
+++ b/app/reports/SY_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/SY_research.xlsx
+++ b/app/reports/SY_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.49</v>
+        <v>2.535</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0524399995803833</v>
+        <v>0.05240000247955322</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>100614277.9116466</v>
+        <v>100614286.3905325</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.49</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>250529552</v>
+        <v>255057216</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>220865120</v>
+        <v>231078528</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>954443456</v>
+        <v>917568704</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>270643840</v>
+        <v>259141264</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>747525952</v>
+        <v>716379072</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>89382080</v>
+        <v>85793272</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>1435460352</v>
+        <v>1425687936</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>16.254097</v>
+        <v>16.143442</v>
       </c>
       <c r="E11" s="33" t="n">
         <v>-22.254</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1693211264</v>
+        <v>1732130048</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">

--- a/app/reports/SY_research.xlsx
+++ b/app/reports/SY_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.535</v>
+        <v>2.625</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05220999717712402</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>100614286.3905325</v>
+        <v>100614278.0952381</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.535</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="38">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>255057216</v>
+        <v>264112480</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>-0.03</v>
@@ -1515,14 +1515,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>231078528</v>
+        <v>217673424</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-4.695</v>
+        <v>-4.872</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>5.528</v>
+        <v>5.737</v>
       </c>
     </row>
     <row r="7">
@@ -1537,11 +1537,11 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>917568704</v>
+        <v>879157376</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-3.011</v>
+        <v>-2.843</v>
       </c>
       <c r="F7" s="33" t="n"/>
     </row>
@@ -1557,14 +1557,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>259141264</v>
+        <v>262870784</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>3.354</v>
+        <v>3.587</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>-2.104</v>
+        <v>-2.251</v>
       </c>
     </row>
     <row r="9">
@@ -1583,10 +1583,10 @@
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-11.405</v>
+        <v>-11.158</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>14.858</v>
+        <v>14.536</v>
       </c>
     </row>
     <row r="10">
@@ -1601,11 +1601,11 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>85793272</v>
+        <v>74463144</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-0.125</v>
+        <v>-0.09</v>
       </c>
       <c r="F10" s="33" t="n"/>
     </row>
@@ -1621,16 +1621,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>1425687936</v>
+        <v>1405057280</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>16.143442</v>
+        <v>15.909836</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>-22.254</v>
+        <v>-22.053</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>41.653</v>
+        <v>41.276</v>
       </c>
     </row>
     <row r="12">
@@ -1669,14 +1669,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1732130048</v>
+        <v>1735012992</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>40.14</v>
+        <v>40.681</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>6.644</v>
+        <v>6.734</v>
       </c>
     </row>
     <row r="15">
